--- a/sales_data.xlsx
+++ b/sales_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PREDATOR\Desktop\Rishan\MY PROJECTS\Sales_Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C6DA0BA-C433-4E17-8C69-DBC9F4886187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F9E8205-B446-41D2-954D-8FC7801DA978}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="pivot tables" sheetId="2" r:id="rId1"/>
@@ -201,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
@@ -212,7 +212,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,10 +478,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="2.3148512685914262E-3"/>
+          <c:x val="1.2037073490813649E-2"/>
           <c:y val="5.7639982502187218E-3"/>
-          <c:w val="0.99768518518518523"/>
-          <c:h val="0.95360326152124386"/>
+          <c:w val="0.98796292650918638"/>
+          <c:h val="0.93375217365819352"/>
         </c:manualLayout>
       </c:layout>
       <c:barChart>
@@ -662,12 +661,9 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr algn="ctr">
-              <a:defRPr sz="900" b="1" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -845,7 +841,7 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -902,7 +898,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -959,7 +955,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -1042,7 +1038,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent6"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1205,13 +1201,10 @@
           <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:pPr algn="ctr">
+              <a:defRPr lang="en-US" sz="1000" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1407,13 +1400,10 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1466,13 +1456,10 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
-          <a:ln w="28575" cap="rnd">
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:round/>
+          <a:ln>
+            <a:noFill/>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
@@ -1526,7 +1513,7 @@
         <c:spPr>
           <a:ln w="28575" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="accent2"/>
             </a:solidFill>
             <a:round/>
           </a:ln>
@@ -1598,7 +1585,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:round/>
             </a:ln>
@@ -1766,10 +1753,7 @@
             <a:pPr>
               <a:defRPr lang="en-US" sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
                 <a:solidFill>
-                  <a:sysClr val="windowText" lastClr="000000">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:sysClr>
+                  <a:sysClr val="windowText" lastClr="000000"/>
                 </a:solidFill>
                 <a:latin typeface="+mn-lt"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1803,7 +1787,7 @@
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="25400">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -1947,7 +1931,7 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -2006,7 +1990,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -2065,7 +2049,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -2079,7 +2063,7 @@
         <c:idx val="3"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -2093,7 +2077,7 @@
         <c:idx val="4"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -2115,15 +2099,18 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="0">
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
-              <a:pPr algn="ctr">
-                <a:defRPr lang="en-US" sz="1100" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1"/>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
                   </a:solidFill>
                   <a:latin typeface="+mn-lt"/>
                   <a:ea typeface="+mn-ea"/>
@@ -2133,9 +2120,8 @@
               <a:endParaRPr lang="en-US"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="bestFit"/>
           <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
+          <c:showVal val="0"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
@@ -2149,7 +2135,7 @@
         <c:idx val="5"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -2162,8 +2148,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="-0.24658812534796795"/>
-              <c:y val="-4.6709755030621275E-2"/>
+              <c:x val="-0.2314366101964527"/>
+              <c:y val="-3.8376421697287888E-2"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -2195,7 +2181,7 @@
           <c:dLblPos val="bestFit"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
-          <c:showCatName val="0"/>
+          <c:showCatName val="1"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
@@ -2203,8 +2189,8 @@
             <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
               <c15:layout>
                 <c:manualLayout>
-                  <c:w val="0.14147717330788198"/>
-                  <c:h val="7.3416666666666672E-2"/>
+                  <c:w val="0.19198222381293248"/>
+                  <c:h val="0.15675"/>
                 </c:manualLayout>
               </c15:layout>
             </c:ext>
@@ -2215,7 +2201,7 @@
         <c:idx val="6"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent1"/>
+            <a:schemeClr val="accent2"/>
           </a:solidFill>
           <a:ln w="19050">
             <a:solidFill>
@@ -2228,8 +2214,8 @@
           <c:idx val="0"/>
           <c:layout>
             <c:manualLayout>
-              <c:x val="0.20050047721307565"/>
-              <c:y val="1.7418635170603675E-2"/>
+              <c:x val="0.22701562872822717"/>
+              <c:y val="2.7140857392825898E-2"/>
             </c:manualLayout>
           </c:layout>
           <c:spPr>
@@ -2241,7 +2227,7 @@
           </c:spPr>
           <c:txPr>
             <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="0">
-              <a:spAutoFit/>
+              <a:noAutofit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
@@ -2261,12 +2247,19 @@
           <c:dLblPos val="bestFit"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="1"/>
-          <c:showCatName val="0"/>
+          <c:showCatName val="1"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout>
+                <c:manualLayout>
+                  <c:w val="0.20021454704525568"/>
+                  <c:h val="0.10238888888888889"/>
+                </c:manualLayout>
+              </c15:layout>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
@@ -2294,7 +2287,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent1"/>
+                <a:schemeClr val="accent2"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -2314,7 +2307,7 @@
             <c:bubble3D val="0"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2"/>
+                <a:schemeClr val="accent4"/>
               </a:solidFill>
               <a:ln w="19050">
                 <a:solidFill>
@@ -2334,8 +2327,8 @@
               <c:idx val="0"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="-0.24658812534796795"/>
-                  <c:y val="-4.6709755030621275E-2"/>
+                  <c:x val="-0.2314366101964527"/>
+                  <c:y val="-3.8376421697287888E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:spPr>
@@ -2367,7 +2360,7 @@
               <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
-              <c:showCatName val="0"/>
+              <c:showCatName val="1"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
@@ -2375,8 +2368,8 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout>
                     <c:manualLayout>
-                      <c:w val="0.14147717330788198"/>
-                      <c:h val="7.3416666666666672E-2"/>
+                      <c:w val="0.19198222381293248"/>
+                      <c:h val="0.15675"/>
                     </c:manualLayout>
                   </c15:layout>
                 </c:ext>
@@ -2389,19 +2382,26 @@
               <c:idx val="1"/>
               <c:layout>
                 <c:manualLayout>
-                  <c:x val="0.20050047721307565"/>
-                  <c:y val="1.7418635170603675E-2"/>
+                  <c:x val="0.22701562872822717"/>
+                  <c:y val="2.7140857392825898E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:dLblPos val="bestFit"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="1"/>
-              <c:showCatName val="0"/>
+              <c:showCatName val="1"/>
               <c:showSerName val="0"/>
               <c:showPercent val="0"/>
               <c:showBubbleSize val="0"/>
               <c:extLst>
-                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                  <c15:layout>
+                    <c:manualLayout>
+                      <c:w val="0.20021454704525568"/>
+                      <c:h val="0.10238888888888889"/>
+                    </c:manualLayout>
+                  </c15:layout>
+                </c:ext>
                 <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
                   <c16:uniqueId val="{00000003-9AA9-432E-8D2A-DB96CF7F0C8A}"/>
                 </c:ext>
@@ -2416,7 +2416,7 @@
             </c:spPr>
             <c:txPr>
               <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="0">
-                <a:spAutoFit/>
+                <a:noAutofit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
@@ -2436,7 +2436,7 @@
             <c:dLblPos val="bestFit"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
-            <c:showCatName val="0"/>
+            <c:showCatName val="1"/>
             <c:showSerName val="0"/>
             <c:showPercent val="0"/>
             <c:showBubbleSize val="0"/>
@@ -2573,13 +2573,10 @@
 </file>
 
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="11">
   <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
   <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
   <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -2613,13 +2610,10 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="13">
+  <a:schemeClr val="accent6"/>
+  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
     <a:lumMod val="60000"/>
@@ -2653,12 +2647,9 @@
 </file>
 
 <file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
@@ -2693,12 +2684,9 @@
 </file>
 
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="12">
   <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
   <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
   <a:schemeClr val="accent6"/>
   <cs:variation/>
   <cs:variation>
@@ -4787,8 +4775,8 @@
     <xdr:to>
       <xdr:col>38</xdr:col>
       <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -5460,252 +5448,6 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{737704CB-BB69-4F57-94E1-482F6E272DC6}" name="City" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
-  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="21">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="7">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="7"/>
-  </rowFields>
-  <rowItems count="7">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i>
-      <x v="3"/>
-    </i>
-    <i>
-      <x v="4"/>
-    </i>
-    <i>
-      <x v="5"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Revenue From each cities" fld="13" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="25" format="2" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB74325C-B3A9-4533-9280-CAA57F4FA558}" name="Category" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
-  <location ref="J13:K16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField numFmtId="164" showAll="0">
-      <items count="21">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="1"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="0"/>
-        <item x="5"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="3">
-        <item x="1"/>
-        <item x="0"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0">
-      <items count="7">
-        <item x="3"/>
-        <item x="2"/>
-        <item x="1"/>
-        <item x="5"/>
-        <item x="0"/>
-        <item x="4"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="4"/>
-  </rowFields>
-  <rowItems count="3">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of Total Revenue" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="3">
-    <chartFormat chart="11" format="4" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="5">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-    <chartFormat chart="11" format="6">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="2">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-          <reference field="4" count="1" selected="0">
-            <x v="1"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3A780F95-F99D-48BF-ADA3-3884FEB3290B}" name="Customer" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="7">
   <location ref="J3:K10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
@@ -5824,7 +5566,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{3EEA5FD6-2AAD-4B44-947C-482D8E7C13B5}" name="Date" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="23">
   <location ref="G3:H24" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
@@ -5975,7 +5717,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B7D9F2EF-6219-4C08-B08D-E25E7814CAEA}" name="Products" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="D3:E9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
@@ -6100,6 +5842,252 @@
 </pivotTableDefinition>
 </file>
 
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{737704CB-BB69-4F57-94E1-482F6E272DC6}" name="City" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="26">
+  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="7"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Revenue From each cities" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="25" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FB74325C-B3A9-4533-9280-CAA57F4FA558}" name="Category" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="J13:K16" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0">
+      <items count="21">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="4"/>
+        <item x="0"/>
+        <item x="5"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="7">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="5"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Total Revenue" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="3">
+    <chartFormat chart="11" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="11" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="4" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Date" xr10:uid="{AE104632-1950-44FB-B691-D3F4ED622BD9}" sourceName="Date">
   <pivotTables>
@@ -6139,7 +6127,7 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Date" xr10:uid="{D5A7955F-D375-4D28-9B2D-7AE51BAD4C3B}" cache="Slicer_Date" caption="Date" rowHeight="234950"/>
+  <slicer name="Date" xr10:uid="{D5A7955F-D375-4D28-9B2D-7AE51BAD4C3B}" cache="Slicer_Date" caption="Date" style="SlicerStyleOther2" rowHeight="234950"/>
 </slicers>
 </file>
 
@@ -6472,13 +6460,13 @@
       <c r="A4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>156400</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4">
         <v>272400</v>
       </c>
       <c r="G4" s="4">
@@ -6490,7 +6478,7 @@
       <c r="J4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="6">
+      <c r="K4">
         <v>56000</v>
       </c>
     </row>
@@ -6498,13 +6486,13 @@
       <c r="A5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>71700</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5">
         <v>674700</v>
       </c>
       <c r="G5" s="4">
@@ -6516,7 +6504,7 @@
       <c r="J5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K5">
         <v>54400</v>
       </c>
     </row>
@@ -6524,13 +6512,13 @@
       <c r="A6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>116000</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6">
         <v>1036700</v>
       </c>
       <c r="G6" s="4">
@@ -6542,7 +6530,7 @@
       <c r="J6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K6">
         <v>68500</v>
       </c>
     </row>
@@ -6550,13 +6538,13 @@
       <c r="A7" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>130000</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7">
         <v>683200</v>
       </c>
       <c r="G7" s="4">
@@ -6568,7 +6556,7 @@
       <c r="J7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7">
         <v>72400</v>
       </c>
     </row>
@@ -6576,13 +6564,13 @@
       <c r="A8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>109600</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8">
         <v>913600</v>
       </c>
       <c r="G8" s="4">
@@ -6594,7 +6582,7 @@
       <c r="J8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="6">
+      <c r="K8">
         <v>80000</v>
       </c>
     </row>
@@ -6602,13 +6590,13 @@
       <c r="A9" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>86500</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9">
         <v>3580600</v>
       </c>
       <c r="G9" s="4">
@@ -6620,7 +6608,7 @@
       <c r="J9" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K9">
         <v>20200</v>
       </c>
     </row>
@@ -6628,7 +6616,7 @@
       <c r="A10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10">
         <v>670200</v>
       </c>
       <c r="G10" s="4">
@@ -6640,7 +6628,7 @@
       <c r="J10" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K10">
         <v>351500</v>
       </c>
     </row>
@@ -6684,7 +6672,7 @@
       <c r="J14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K14" s="6">
+      <c r="K14">
         <v>1860700</v>
       </c>
     </row>
@@ -6698,7 +6686,7 @@
       <c r="J15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K15" s="6">
+      <c r="K15">
         <v>1719900</v>
       </c>
     </row>
@@ -6712,7 +6700,7 @@
       <c r="J16" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="K16" s="6">
+      <c r="K16">
         <v>3580600</v>
       </c>
     </row>
